--- a/Horarios/HorarioWAN_Ago26.xlsx
+++ b/Horarios/HorarioWAN_Ago26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecmx-my.sharepoint.com/personal/lperezf_tec_mx/Documents/Documents/GitLiz/WAN/Horarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{798E0948-AF01-42C7-8EE1-9DCC2943AE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="14_{798E0948-AF01-42C7-8EE1-9DCC2943AE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3005A30F-6D7F-4A8D-8F71-60A7BA008E32}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="29">
   <si>
     <t>MARTES</t>
   </si>
@@ -238,7 +238,13 @@
     </r>
   </si>
   <si>
-    <t>PRESENTACIÓN DEL RETO CON EL SOCIO FORMADOR / VISITA</t>
+    <t>PRESENTACIÓN DEL RETO CON EL SOCIO FORMADOR</t>
+  </si>
+  <si>
+    <t>RETO: TRABAJO CON EL SOCIO FORMADOR</t>
+  </si>
+  <si>
+    <t>VISITA AL SOCIO FORMADOR</t>
   </si>
 </sst>
 </file>
@@ -402,49 +408,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -810,13 +816,13 @@
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -824,19 +830,21 @@
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="15"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="11" t="s">
+      <c r="D5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>5</v>
       </c>
     </row>
@@ -844,9 +852,9 @@
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="12"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -866,35 +874,33 @@
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>3</v>
+      <c r="C9" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="12"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="11" t="s">
+      <c r="D11" s="24"/>
+      <c r="E11" s="15" t="s">
         <v>5</v>
       </c>
     </row>
@@ -902,9 +908,9 @@
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="16"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
@@ -921,13 +927,13 @@
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="C15" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -935,21 +941,21 @@
       <c r="B16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="16"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="15" t="s">
         <v>5</v>
       </c>
     </row>
@@ -957,9 +963,9 @@
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
@@ -976,13 +982,13 @@
       <c r="B21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -990,19 +996,19 @@
       <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="11" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="15" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1010,9 +1016,9 @@
       <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
     </row>
     <row r="26" spans="2:5" s="9" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="7" t="s">
@@ -1026,35 +1032,35 @@
       <c r="B27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>3</v>
+      <c r="C27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="24"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="12"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="13" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1062,9 +1068,9 @@
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
@@ -1084,32 +1090,32 @@
       <c r="B33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>3</v>
+      <c r="C33" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
       <c r="E34" s="26"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E35" s="26"/>
@@ -1118,8 +1124,8 @@
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="E36" s="27"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.35">
@@ -1140,13 +1146,13 @@
       <c r="B39" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="14" t="s">
+      <c r="C39" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1154,21 +1160,21 @@
       <c r="B40" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1176,9 +1182,9 @@
       <c r="B42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="13"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="22"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="5"/>
@@ -1198,35 +1204,35 @@
       <c r="B45" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E45" s="22" t="s">
         <v>3</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="14" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C46" s="13"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="22"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D47" s="19" t="s">
+      <c r="D47" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="20" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1234,9 +1240,9 @@
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="22"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B49" s="5"/>
@@ -1252,17 +1258,17 @@
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D51" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1270,19 +1276,19 @@
       <c r="B52" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="13"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="22"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B53" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="19" t="s">
+      <c r="C53" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="D53" s="28"/>
+      <c r="E53" s="13" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1290,9 +1296,9 @@
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C54" s="27"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="14"/>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B55" s="5"/>
@@ -1312,13 +1318,13 @@
       <c r="B57" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="25" t="s">
+      <c r="C57" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D57" s="25" t="s">
+      <c r="D57" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E57" s="25" t="s">
+      <c r="E57" s="23" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1354,10 +1360,9 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="C45:C46"/>
-    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="D57:D60"/>
     <mergeCell ref="E57:E60"/>
     <mergeCell ref="C41:C42"/>
@@ -1368,11 +1373,9 @@
     <mergeCell ref="D47:D48"/>
     <mergeCell ref="E47:E48"/>
     <mergeCell ref="C57:C60"/>
-    <mergeCell ref="C51:C54"/>
-    <mergeCell ref="D51:D52"/>
     <mergeCell ref="E51:E52"/>
-    <mergeCell ref="D53:D54"/>
     <mergeCell ref="E53:E54"/>
+    <mergeCell ref="D51:D54"/>
     <mergeCell ref="E17:E18"/>
     <mergeCell ref="C39:C40"/>
     <mergeCell ref="D39:D40"/>
@@ -1386,27 +1389,30 @@
     <mergeCell ref="E33:E36"/>
     <mergeCell ref="C35:C36"/>
     <mergeCell ref="D35:D36"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E29:E30"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="D21:D22"/>
     <mergeCell ref="E21:E22"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="D15:D16"/>
     <mergeCell ref="E15:E16"/>
     <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="C51:C52"/>
+    <mergeCell ref="C53:C54"/>
     <mergeCell ref="C17:C18"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="C21:C24"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C45:C46"/>
+    <mergeCell ref="C47:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="73" orientation="portrait" r:id="rId1"/>
